--- a/input/02_market_characterization.xlsx
+++ b/input/02_market_characterization.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_0FEFC881A94BB305686407648BA328F33CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66A5574B-1D4C-4D1A-B866-024E99076757}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_0FEFC881A94BB305686407648BA328F33CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12CD19FA-1B96-4B0E-A811-589F20DC1716}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,10 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
-  <si>
-    <t>utility</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
   <si>
     <t>single_family</t>
   </si>
@@ -81,9 +78,6 @@
     <t>multi_family_li</t>
   </si>
   <si>
-    <t>test_utility</t>
-  </si>
-  <si>
     <t>competition_group</t>
   </si>
   <si>
@@ -166,6 +160,33 @@
   </si>
   <si>
     <t>whole_home_insultation_efficient_residential</t>
+  </si>
+  <si>
+    <t>electric_utility</t>
+  </si>
+  <si>
+    <t>gas_utility</t>
+  </si>
+  <si>
+    <t>test_utility_1</t>
+  </si>
+  <si>
+    <t>test_utility_2</t>
+  </si>
+  <si>
+    <t>multifamily</t>
+  </si>
+  <si>
+    <t>multifamily_li</t>
+  </si>
+  <si>
+    <t>insulation_natural_gas_efficient_residential</t>
+  </si>
+  <si>
+    <t>HERS_electric_efficient_residential</t>
+  </si>
+  <si>
+    <t>HERS_electric_baseline_residential</t>
   </si>
 </sst>
 </file>
@@ -175,13 +196,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000\ ;\(#,##0.000\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -204,13 +238,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,26 +582,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -592,20 +635,143 @@
       <c r="AE1" s="1"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="4">
+        <v>50000</v>
+      </c>
+      <c r="D2" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E2" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="4">
         <v>100000</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D3" s="4">
         <v>50000</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E3" s="4">
         <v>20000</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F3" s="4">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4">
+        <v>275000</v>
+      </c>
+      <c r="D4" s="4">
+        <v>47000</v>
+      </c>
+      <c r="E4" s="4">
+        <v>19000</v>
+      </c>
+      <c r="F4" s="4">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4">
+        <v>50000</v>
+      </c>
+      <c r="D5" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4">
+        <v>55000</v>
+      </c>
+      <c r="D6" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E6" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="4">
+        <v>40000</v>
+      </c>
+      <c r="D7" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E7" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="4">
+        <v>55000</v>
+      </c>
+      <c r="D8" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E8" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
@@ -628,30 +794,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>0.2</v>
@@ -668,10 +834,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
       </c>
       <c r="C3">
         <v>0.2</v>
@@ -688,10 +854,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0.3</v>
@@ -708,10 +874,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>0.7</v>
@@ -728,10 +894,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>0.2</v>
@@ -748,10 +914,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -768,10 +934,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -794,7 +960,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C04C4BE-F391-4F13-A40F-522BD97AD2C9}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -808,370 +974,462 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D6" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3">
         <v>0.2</v>
       </c>
-      <c r="E2">
-        <v>0.1</v>
-      </c>
-      <c r="F2">
+      <c r="E17" s="3">
         <v>0.2</v>
       </c>
-      <c r="G2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
+      <c r="F17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3">
         <v>0.5</v>
       </c>
-      <c r="E3">
-        <v>0.6</v>
-      </c>
-      <c r="F3">
+      <c r="E19" s="3">
         <v>0.5</v>
       </c>
-      <c r="G3">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
+      <c r="F19" s="3">
         <v>0.5</v>
       </c>
-      <c r="E4">
-        <v>0.4</v>
-      </c>
-      <c r="F4">
-        <v>0.4</v>
-      </c>
-      <c r="G4">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>0.7</v>
-      </c>
-      <c r="E5">
-        <v>0.7</v>
-      </c>
-      <c r="F5">
-        <v>0.6</v>
-      </c>
-      <c r="G5">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>0.3</v>
-      </c>
-      <c r="E6">
-        <v>0.1</v>
-      </c>
-      <c r="F6">
-        <v>0.1</v>
-      </c>
-      <c r="G6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7">
-        <v>0.7</v>
-      </c>
-      <c r="E7">
-        <v>1.2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>0.3</v>
-      </c>
-      <c r="E8">
-        <v>0.3</v>
-      </c>
-      <c r="F8">
-        <v>0.3</v>
-      </c>
-      <c r="G8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="G19" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D10">
-        <v>0.25</v>
-      </c>
-      <c r="E10">
-        <v>0.25</v>
-      </c>
-      <c r="F10">
-        <v>0.25</v>
-      </c>
-      <c r="G10">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11">
-        <v>0.25</v>
-      </c>
-      <c r="E11">
-        <v>0.25</v>
-      </c>
-      <c r="F11">
-        <v>0.25</v>
-      </c>
-      <c r="G11">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12">
-        <v>0.25</v>
-      </c>
-      <c r="E12">
-        <v>0.25</v>
-      </c>
-      <c r="F12">
-        <v>0.25</v>
-      </c>
-      <c r="G12">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13">
-        <v>0.25</v>
-      </c>
-      <c r="E13">
-        <v>0.25</v>
-      </c>
-      <c r="F13">
-        <v>0.25</v>
-      </c>
-      <c r="G13">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14">
+      <c r="D20" s="3">
         <v>0.5</v>
       </c>
-      <c r="E14">
+      <c r="E20" s="3">
         <v>0.5</v>
       </c>
-      <c r="F14">
+      <c r="F20" s="3">
         <v>0.5</v>
       </c>
-      <c r="G14">
+      <c r="G20" s="3">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15">
-        <v>0.25</v>
-      </c>
-      <c r="E15">
-        <v>0.25</v>
-      </c>
-      <c r="F15">
-        <v>0.25</v>
-      </c>
-      <c r="G15">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16">
-        <v>0.25</v>
-      </c>
-      <c r="E16">
-        <v>0.25</v>
-      </c>
-      <c r="F16">
-        <v>0.25</v>
-      </c>
-      <c r="G16">
-        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1180,12 +1438,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1194,7 +1446,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1019b97992c14b0ad4b597aaa0d4ffdf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bfcefbd2d97d1dabd843dc4e1de334f1" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -1338,16 +1590,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD392A7-7BA8-4912-9645-25D1BF77DA47}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F24D1065-9B3E-4F3B-A1F3-390BA331B399}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1355,7 +1604,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56E778D5-A61F-4975-B41D-A8B9D2EC63D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1371,4 +1620,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD392A7-7BA8-4912-9645-25D1BF77DA47}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>